--- a/e_commerce_forms/015_personalized_notebook_order_form--e_commerce_forms.xlsx
+++ b/e_commerce_forms/015_personalized_notebook_order_form--e_commerce_forms.xlsx
@@ -1,15 +1,15 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="survey" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet name="choices" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet name="settings" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="survey" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="choices" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="settings" sheetId="3" state="visible" r:id="rId3"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -437,12 +437,12 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E36"/>
+  <dimension ref="A1:E18"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="12" customWidth="1" min="1" max="1"/>
-    <col width="25" customWidth="1" min="2" max="2"/>
-    <col width="25" customWidth="1" min="3" max="3"/>
+    <col width="21" customWidth="1" min="2" max="2"/>
+    <col width="17" customWidth="1" min="3" max="3"/>
     <col width="6" customWidth="1" min="4" max="4"/>
     <col width="10" customWidth="1" min="5" max="5"/>
   </cols>
@@ -543,12 +543,12 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>notebook_info</t>
+          <t>customer_email</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>Notebook Info</t>
+          <t>Customer Email</t>
         </is>
       </c>
       <c r="D5" t="inlineStr"/>
@@ -561,17 +561,17 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>text</t>
+          <t>select_one</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>shipping_details</t>
+          <t>shipping_method</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>Shipping Details</t>
+          <t>Shipping Method</t>
         </is>
       </c>
       <c r="D6" t="inlineStr"/>
@@ -589,12 +589,12 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>order_summary</t>
+          <t>customer_notes</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>Order Summary</t>
+          <t>Customer Notes</t>
         </is>
       </c>
       <c r="D7" t="inlineStr"/>
@@ -612,12 +612,12 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>payment_info</t>
+          <t>order_total</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>Payment Info</t>
+          <t>Order Total</t>
         </is>
       </c>
       <c r="D8" t="inlineStr"/>
@@ -635,12 +635,12 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>customer_info_address</t>
+          <t>order_shipping</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>Customer Address</t>
+          <t>Shipping Amount</t>
         </is>
       </c>
       <c r="D9" t="inlineStr"/>
@@ -653,17 +653,17 @@
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>text</t>
+          <t>select_one</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>order_total</t>
+          <t>notebook_color</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>Order Total</t>
+          <t>Color</t>
         </is>
       </c>
       <c r="D10" t="inlineStr"/>
@@ -676,17 +676,17 @@
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>text</t>
+          <t>select_one</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>order_total_shipping</t>
+          <t>notebook_cover_type</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>Order Total Shipping</t>
+          <t>Cover Type</t>
         </is>
       </c>
       <c r="D11" t="inlineStr"/>
@@ -699,17 +699,17 @@
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>text</t>
+          <t>select_one</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>order_summary_2</t>
+          <t>payment_method</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>Order Summary 2</t>
+          <t>Payment Method</t>
         </is>
       </c>
       <c r="D12" t="inlineStr"/>
@@ -727,12 +727,12 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>payment_info_2</t>
+          <t>customer_info_2</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>Payment Info 2</t>
+          <t>Customer Info 2</t>
         </is>
       </c>
       <c r="D13" t="inlineStr"/>
@@ -750,12 +750,12 @@
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>customer_info_2</t>
+          <t>order_details</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>Customer Info 2</t>
+          <t>Order Details</t>
         </is>
       </c>
       <c r="D14" t="inlineStr"/>
@@ -768,17 +768,17 @@
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>text</t>
+          <t>select_one</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>customer_name</t>
+          <t>customer_country</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>Customer Name</t>
+          <t>Country</t>
         </is>
       </c>
       <c r="D15" t="inlineStr"/>
@@ -791,17 +791,17 @@
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>text</t>
+          <t>select_one</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>customer_email</t>
+          <t>customer_city</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>Customer Email</t>
+          <t>City</t>
         </is>
       </c>
       <c r="D16" t="inlineStr"/>
@@ -814,17 +814,17 @@
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>text</t>
+          <t>select_one</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>customer_phone</t>
+          <t>customer_country_2</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>Customer Phone</t>
+          <t>Country 2</t>
         </is>
       </c>
       <c r="D17" t="inlineStr"/>
@@ -842,430 +842,16 @@
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>customer_country</t>
+          <t>customer_city_2</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>Customer Country</t>
+          <t>City 2</t>
         </is>
       </c>
       <c r="D18" t="inlineStr"/>
       <c r="E18" t="inlineStr">
-        <is>
-          <t>no</t>
-        </is>
-      </c>
-    </row>
-    <row r="19">
-      <c r="A19" t="inlineStr">
-        <is>
-          <t>select_one</t>
-        </is>
-      </c>
-      <c r="B19" t="inlineStr">
-        <is>
-          <t>customer_city</t>
-        </is>
-      </c>
-      <c r="C19" t="inlineStr">
-        <is>
-          <t>Customer City</t>
-        </is>
-      </c>
-      <c r="D19" t="inlineStr"/>
-      <c r="E19" t="inlineStr">
-        <is>
-          <t>no</t>
-        </is>
-      </c>
-    </row>
-    <row r="20">
-      <c r="A20" t="inlineStr">
-        <is>
-          <t>select_one</t>
-        </is>
-      </c>
-      <c r="B20" t="inlineStr">
-        <is>
-          <t>notebook_color</t>
-        </is>
-      </c>
-      <c r="C20" t="inlineStr">
-        <is>
-          <t>Notebook Color</t>
-        </is>
-      </c>
-      <c r="D20" t="inlineStr"/>
-      <c r="E20" t="inlineStr">
-        <is>
-          <t>no</t>
-        </is>
-      </c>
-    </row>
-    <row r="21">
-      <c r="A21" t="inlineStr">
-        <is>
-          <t>select_one</t>
-        </is>
-      </c>
-      <c r="B21" t="inlineStr">
-        <is>
-          <t>notebook_cover_type</t>
-        </is>
-      </c>
-      <c r="C21" t="inlineStr">
-        <is>
-          <t>Notebook Cover Type</t>
-        </is>
-      </c>
-      <c r="D21" t="inlineStr"/>
-      <c r="E21" t="inlineStr">
-        <is>
-          <t>no</t>
-        </is>
-      </c>
-    </row>
-    <row r="22">
-      <c r="A22" t="inlineStr">
-        <is>
-          <t>text</t>
-        </is>
-      </c>
-      <c r="B22" t="inlineStr">
-        <is>
-          <t>customer_notes</t>
-        </is>
-      </c>
-      <c r="C22" t="inlineStr">
-        <is>
-          <t>Customer Notes</t>
-        </is>
-      </c>
-      <c r="D22" t="inlineStr"/>
-      <c r="E22" t="inlineStr">
-        <is>
-          <t>no</t>
-        </is>
-      </c>
-    </row>
-    <row r="23">
-      <c r="A23" t="inlineStr">
-        <is>
-          <t>text</t>
-        </is>
-      </c>
-      <c r="B23" t="inlineStr">
-        <is>
-          <t>order_total_amount</t>
-        </is>
-      </c>
-      <c r="C23" t="inlineStr">
-        <is>
-          <t>Order Total Amount</t>
-        </is>
-      </c>
-      <c r="D23" t="inlineStr"/>
-      <c r="E23" t="inlineStr">
-        <is>
-          <t>no</t>
-        </is>
-      </c>
-    </row>
-    <row r="24">
-      <c r="A24" t="inlineStr">
-        <is>
-          <t>text</t>
-        </is>
-      </c>
-      <c r="B24" t="inlineStr">
-        <is>
-          <t>order_shipping_amount</t>
-        </is>
-      </c>
-      <c r="C24" t="inlineStr">
-        <is>
-          <t>Order Shipping Amount</t>
-        </is>
-      </c>
-      <c r="D24" t="inlineStr"/>
-      <c r="E24" t="inlineStr">
-        <is>
-          <t>no</t>
-        </is>
-      </c>
-    </row>
-    <row r="25">
-      <c r="A25" t="inlineStr">
-        <is>
-          <t>text</t>
-        </is>
-      </c>
-      <c r="B25" t="inlineStr">
-        <is>
-          <t>customer_notes_2</t>
-        </is>
-      </c>
-      <c r="C25" t="inlineStr">
-        <is>
-          <t>Customer Notes 2</t>
-        </is>
-      </c>
-      <c r="D25" t="inlineStr"/>
-      <c r="E25" t="inlineStr">
-        <is>
-          <t>no</t>
-        </is>
-      </c>
-    </row>
-    <row r="26">
-      <c r="A26" t="inlineStr">
-        <is>
-          <t>text</t>
-        </is>
-      </c>
-      <c r="B26" t="inlineStr">
-        <is>
-          <t>order_total_amount_2</t>
-        </is>
-      </c>
-      <c r="C26" t="inlineStr">
-        <is>
-          <t>Order Total Amount 2</t>
-        </is>
-      </c>
-      <c r="D26" t="inlineStr"/>
-      <c r="E26" t="inlineStr">
-        <is>
-          <t>no</t>
-        </is>
-      </c>
-    </row>
-    <row r="27">
-      <c r="A27" t="inlineStr">
-        <is>
-          <t>text</t>
-        </is>
-      </c>
-      <c r="B27" t="inlineStr">
-        <is>
-          <t>order_shipping_amount_2</t>
-        </is>
-      </c>
-      <c r="C27" t="inlineStr">
-        <is>
-          <t>Order Shipping Amount 2</t>
-        </is>
-      </c>
-      <c r="D27" t="inlineStr"/>
-      <c r="E27" t="inlineStr">
-        <is>
-          <t>no</t>
-        </is>
-      </c>
-    </row>
-    <row r="28">
-      <c r="A28" t="inlineStr">
-        <is>
-          <t>select_one</t>
-        </is>
-      </c>
-      <c r="B28" t="inlineStr">
-        <is>
-          <t>payment_method</t>
-        </is>
-      </c>
-      <c r="C28" t="inlineStr">
-        <is>
-          <t>Payment Method</t>
-        </is>
-      </c>
-      <c r="D28" t="inlineStr"/>
-      <c r="E28" t="inlineStr">
-        <is>
-          <t>no</t>
-        </is>
-      </c>
-    </row>
-    <row r="29">
-      <c r="A29" t="inlineStr">
-        <is>
-          <t>select_one</t>
-        </is>
-      </c>
-      <c r="B29" t="inlineStr">
-        <is>
-          <t>customer_country_2</t>
-        </is>
-      </c>
-      <c r="C29" t="inlineStr">
-        <is>
-          <t>Customer Country 2</t>
-        </is>
-      </c>
-      <c r="D29" t="inlineStr"/>
-      <c r="E29" t="inlineStr">
-        <is>
-          <t>no</t>
-        </is>
-      </c>
-    </row>
-    <row r="30">
-      <c r="A30" t="inlineStr">
-        <is>
-          <t>select_one</t>
-        </is>
-      </c>
-      <c r="B30" t="inlineStr">
-        <is>
-          <t>customer_city_2</t>
-        </is>
-      </c>
-      <c r="C30" t="inlineStr">
-        <is>
-          <t>Customer City 2</t>
-        </is>
-      </c>
-      <c r="D30" t="inlineStr"/>
-      <c r="E30" t="inlineStr">
-        <is>
-          <t>no</t>
-        </is>
-      </c>
-    </row>
-    <row r="31">
-      <c r="A31" t="inlineStr">
-        <is>
-          <t>text</t>
-        </is>
-      </c>
-      <c r="B31" t="inlineStr">
-        <is>
-          <t>customer_info_2</t>
-        </is>
-      </c>
-      <c r="C31" t="inlineStr">
-        <is>
-          <t>Customer Info 2</t>
-        </is>
-      </c>
-      <c r="D31" t="inlineStr"/>
-      <c r="E31" t="inlineStr">
-        <is>
-          <t>no</t>
-        </is>
-      </c>
-    </row>
-    <row r="32">
-      <c r="A32" t="inlineStr">
-        <is>
-          <t>text</t>
-        </is>
-      </c>
-      <c r="B32" t="inlineStr">
-        <is>
-          <t>customer_notes_2</t>
-        </is>
-      </c>
-      <c r="C32" t="inlineStr">
-        <is>
-          <t>Customer Notes 2</t>
-        </is>
-      </c>
-      <c r="D32" t="inlineStr"/>
-      <c r="E32" t="inlineStr">
-        <is>
-          <t>no</t>
-        </is>
-      </c>
-    </row>
-    <row r="33">
-      <c r="A33" t="inlineStr">
-        <is>
-          <t>text</t>
-        </is>
-      </c>
-      <c r="B33" t="inlineStr">
-        <is>
-          <t>order_total</t>
-        </is>
-      </c>
-      <c r="C33" t="inlineStr">
-        <is>
-          <t>Order Total</t>
-        </is>
-      </c>
-      <c r="D33" t="inlineStr"/>
-      <c r="E33" t="inlineStr">
-        <is>
-          <t>no</t>
-        </is>
-      </c>
-    </row>
-    <row r="34">
-      <c r="A34" t="inlineStr">
-        <is>
-          <t>text</t>
-        </is>
-      </c>
-      <c r="B34" t="inlineStr">
-        <is>
-          <t>order_shipping</t>
-        </is>
-      </c>
-      <c r="C34" t="inlineStr">
-        <is>
-          <t>Order Shipping</t>
-        </is>
-      </c>
-      <c r="D34" t="inlineStr"/>
-      <c r="E34" t="inlineStr">
-        <is>
-          <t>no</t>
-        </is>
-      </c>
-    </row>
-    <row r="35">
-      <c r="A35" t="inlineStr">
-        <is>
-          <t>text</t>
-        </is>
-      </c>
-      <c r="B35" t="inlineStr">
-        <is>
-          <t>order_total_2</t>
-        </is>
-      </c>
-      <c r="C35" t="inlineStr">
-        <is>
-          <t>Order Total 2</t>
-        </is>
-      </c>
-      <c r="D35" t="inlineStr"/>
-      <c r="E35" t="inlineStr">
-        <is>
-          <t>no</t>
-        </is>
-      </c>
-    </row>
-    <row r="36">
-      <c r="A36" t="inlineStr">
-        <is>
-          <t>text</t>
-        </is>
-      </c>
-      <c r="B36" t="inlineStr">
-        <is>
-          <t>order_shipping_2</t>
-        </is>
-      </c>
-      <c r="C36" t="inlineStr">
-        <is>
-          <t>Order Shipping 2</t>
-        </is>
-      </c>
-      <c r="D36" t="inlineStr"/>
-      <c r="E36" t="inlineStr">
         <is>
           <t>no</t>
         </is>
@@ -1282,12 +868,12 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:C28"/>
+  <dimension ref="A1:C31"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="29" customWidth="1" min="1" max="1"/>
-    <col width="36" customWidth="1" min="2" max="2"/>
-    <col width="36" customWidth="1" min="3" max="3"/>
+    <col width="15" customWidth="1" min="2" max="2"/>
+    <col width="15" customWidth="1" min="3" max="3"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -1310,374 +896,374 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>customer_country_choices</t>
+          <t>shipping_method_choices</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>{'id':_1,_'name':_'australia'}</t>
+          <t>credit_card</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>{'id': 1, 'name': 'Australia'}</t>
+          <t>Credit Card</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>customer_country_choices</t>
+          <t>shipping_method_choices</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>{'id':_2,_'name':_'new_zealand'}</t>
+          <t>paypal</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>{'id': 2, 'name': 'New Zealand'}</t>
+          <t>PayPal</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>customer_country_choices</t>
+          <t>shipping_method_choices</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>{'id':_3,_'name':_'usa'}</t>
+          <t>bank_transfer</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>{'id': 3, 'name': 'USA'}</t>
+          <t>Bank Transfer</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>customer_country_choices</t>
+          <t>notebook_color_choices</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>{'id':_4,_'name':_'canada'}</t>
+          <t>black</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>{'id': 4, 'name': 'Canada'}</t>
+          <t>Black</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>customer_city_choices</t>
+          <t>notebook_color_choices</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>{'id':_1,_'name':_'sydney'}</t>
+          <t>red</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>{'id': 1, 'name': 'Sydney'}</t>
+          <t>Red</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>customer_city_choices</t>
+          <t>notebook_color_choices</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>{'id':_2,_'name':_'auckland'}</t>
+          <t>blue</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>{'id': 2, 'name': 'Auckland'}</t>
+          <t>Blue</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>customer_city_choices</t>
+          <t>notebook_color_choices</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>{'id':_3,_'name':_'new_york'}</t>
+          <t>green</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>{'id': 3, 'name': 'New York'}</t>
+          <t>Green</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>customer_city_choices</t>
+          <t>notebook_cover_type_choices</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>{'id':_4,_'name':_'toronto'}</t>
+          <t>plain</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>{'id': 4, 'name': 'Toronto'}</t>
+          <t>Plain</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>notebook_color_choices</t>
+          <t>notebook_cover_type_choices</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>{'id':_1,_'name':_'black'}</t>
+          <t>printed</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>{'id': 1, 'name': 'Black'}</t>
+          <t>Printed</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>notebook_color_choices</t>
+          <t>notebook_cover_type_choices</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>{'id':_2,_'name':_'red'}</t>
+          <t>leather</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>{'id': 2, 'name': 'Red'}</t>
+          <t>Leather</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>notebook_color_choices</t>
+          <t>notebook_cover_type_choices</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>{'id':_3,_'name':_'blue'}</t>
+          <t>cloth</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>{'id': 3, 'name': 'Blue'}</t>
+          <t>Cloth</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>notebook_color_choices</t>
+          <t>payment_method_choices</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>{'id':_4,_'name':_'green'}</t>
+          <t>credit_card</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>{'id': 4, 'name': 'Green'}</t>
+          <t>Credit Card</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>notebook_cover_type_choices</t>
+          <t>payment_method_choices</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>{'id':_1,_'name':_'plain'}</t>
+          <t>paypal</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>{'id': 1, 'name': 'Plain'}</t>
+          <t>PayPal</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>notebook_cover_type_choices</t>
+          <t>payment_method_choices</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>{'id':_2,_'name':_'printed'}</t>
+          <t>bank_transfer</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>{'id': 2, 'name': 'Printed'}</t>
+          <t>Bank Transfer</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>notebook_cover_type_choices</t>
+          <t>customer_country_choices</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>{'id':_3,_'name':_'leather'}</t>
+          <t>australia</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>{'id': 3, 'name': 'Leather'}</t>
+          <t>Australia</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>notebook_cover_type_choices</t>
+          <t>customer_country_choices</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>{'id':_4,_'name':_'cloth'}</t>
+          <t>new_zealand</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>{'id': 4, 'name': 'Cloth'}</t>
+          <t>New Zealand</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>payment_method_choices</t>
+          <t>customer_country_choices</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>{'id':_1,_'name':_'credit_card'}</t>
+          <t>usa</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>{'id': 1, 'name': 'Credit Card'}</t>
+          <t>USA</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>payment_method_choices</t>
+          <t>customer_country_choices</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>{'id':_2,_'name':_'paypal'}</t>
+          <t>canada</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>{'id': 2, 'name': 'PayPal'}</t>
+          <t>Canada</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>payment_method_choices</t>
+          <t>customer_city_choices</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>{'id':_3,_'name':_'bank_transfer'}</t>
+          <t>sydney</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>{'id': 3, 'name': 'Bank Transfer'}</t>
+          <t>Sydney</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>customer_country_2_choices</t>
+          <t>customer_city_choices</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>{'id':_1,_'name':_'australia'}</t>
+          <t>auckland</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>{'id': 1, 'name': 'Australia'}</t>
+          <t>Auckland</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>customer_country_2_choices</t>
+          <t>customer_city_choices</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>{'id':_2,_'name':_'new_zealand'}</t>
+          <t>new_york</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>{'id': 2, 'name': 'New Zealand'}</t>
+          <t>New York</t>
         </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>customer_country_2_choices</t>
+          <t>customer_city_choices</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>{'id':_3,_'name':_'usa'}</t>
+          <t>toronto</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>{'id': 3, 'name': 'USA'}</t>
+          <t>Toronto</t>
         </is>
       </c>
     </row>
@@ -1689,63 +1275,63 @@
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>{'id':_4,_'name':_'canada'}</t>
+          <t>australia</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>{'id': 4, 'name': 'Canada'}</t>
+          <t>Australia</t>
         </is>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>customer_city_2_choices</t>
+          <t>customer_country_2_choices</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>{'id':_1,_'name':_'sydney'}</t>
+          <t>new_zealand</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>{'id': 1, 'name': 'Sydney'}</t>
+          <t>New Zealand</t>
         </is>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>customer_city_2_choices</t>
+          <t>customer_country_2_choices</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>{'id':_2,_'name':_'auckland'}</t>
+          <t>usa</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>{'id': 2, 'name': 'Auckland'}</t>
+          <t>USA</t>
         </is>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>customer_city_2_choices</t>
+          <t>customer_country_2_choices</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>{'id':_3,_'name':_'new_york'}</t>
+          <t>canada</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>{'id': 3, 'name': 'New York'}</t>
+          <t>Canada</t>
         </is>
       </c>
     </row>
@@ -1757,12 +1343,63 @@
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>{'id':_4,_'name':_'toronto'}</t>
+          <t>sydney</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>{'id': 4, 'name': 'Toronto'}</t>
+          <t>Sydney</t>
+        </is>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" t="inlineStr">
+        <is>
+          <t>customer_city_2_choices</t>
+        </is>
+      </c>
+      <c r="B29" t="inlineStr">
+        <is>
+          <t>auckland</t>
+        </is>
+      </c>
+      <c r="C29" t="inlineStr">
+        <is>
+          <t>Auckland</t>
+        </is>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" t="inlineStr">
+        <is>
+          <t>customer_city_2_choices</t>
+        </is>
+      </c>
+      <c r="B30" t="inlineStr">
+        <is>
+          <t>new_york</t>
+        </is>
+      </c>
+      <c r="C30" t="inlineStr">
+        <is>
+          <t>New York</t>
+        </is>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" t="inlineStr">
+        <is>
+          <t>customer_city_2_choices</t>
+        </is>
+      </c>
+      <c r="B31" t="inlineStr">
+        <is>
+          <t>toronto</t>
+        </is>
+      </c>
+      <c r="C31" t="inlineStr">
+        <is>
+          <t>Toronto</t>
         </is>
       </c>
     </row>
